--- a/accor/data/hotels_produits_nettoyes.xlsx
+++ b/accor/data/hotels_produits_nettoyes.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poulet AU Curry Rouge</t>
+          <t>Poulet au Curry Rouge</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ravioli Ricotta Epinard A LA Fiorentina</t>
+          <t>Ravioli Ricotta Epinard a la Fiorentina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Serviettes LOVE &amp; Green BIO X 2</t>
+          <t>Serviettes Love &amp; Green BIO x 2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>WRAP Poulet Texmex</t>
+          <t>Wrap Poulet Texmex</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boardshort Hendaia ECO NT BLEU</t>
+          <t>Boardshort Hendaia Eco NT Bleu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Serviette DE BAIN Microfibre Orange Taille XL 110 X 175 CM</t>
+          <t>Serviette de Bain Microfibre Orange Taille XL 110 x 175 Cm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Coca-Cola SLIM BTE 33cl</t>
+          <t>Coca-Cola Slim BTE 33cl</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chips DE Poulet ROTI 45g</t>
+          <t>Chips de Poulet Roti 45g</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chips Lay's SEL 45g</t>
+          <t>Chips Lay's Sel 45g</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SET Raquettes Beach Tennis Woody Racket White</t>
+          <t>Set Raquettes Beach Tennis Woody Racket White</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaussettes de Sport Enfant Mi-Hautes Artengo Rs 500 Noir (lot de 3) - 31 / 34</t>
+          <t>Chaussettes de Sport Enfant Mi-Hautes Artengo RS 500 Noir (lot de 3) - 31 / 34</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte - Aquashoes 100 GRI 44-45 UK 9.5-10.5</t>
+          <t>Chaussures Aquatiques Adulte - Aquashoes 100 Gri 44-45 UK 9.5-10.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Short BLEU Marine XL</t>
+          <t>Short Bleu Marine XL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SUGARY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>100g Chips Truffe MPG</t>
+          <t>100g Chips Truffe Mpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MPG 180g Houmous Pois Chiche</t>
+          <t>Mpg 180g Houmous Pois Chiche</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sac de Courses DD Paris (moulin Rouge)</t>
+          <t>Sac de Courses Dd Paris (moulin Rouge)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Crayons DE Couleur</t>
+          <t>Crayons de Couleur</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bière Bacchante Power PLAY IPA</t>
+          <t>Bière Bacchante Power Play IPA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO 33cl</t>
+          <t>Coca-Cola Zero 33cl</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>COSMETIQUE</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PAP</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tablettes 30g OUI</t>
+          <t>Tablettes 30g Oui</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gamelle Céramique 17 CM</t>
+          <t>Gamelle Céramique 17 Cm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sandwich Complet THON OEUF 125g</t>
+          <t>Sandwich Complet Thon Oeuf 125g</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pasta BOX Ricotta Epinard</t>
+          <t>Pasta Box Ricotta Epinard</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Red Bull Regular 25 CL</t>
+          <t>Red Bull Regular 25 Cl</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Suedois THON Tomates Marinees 125g</t>
+          <t>Suedois Thon Tomates Marinees 125g</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pasta BOX Saumon</t>
+          <t>Pasta Box Saumon</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>LOAF Banane NOIX 85g</t>
+          <t>Loaf Banane Noix 85g</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>JUS D'Orange</t>
+          <t>Jus D'Orange</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Chips DE Poulet ROTI 45g</t>
+          <t>Chips de Poulet Roti 45g</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>CLUB Poulet Mayonnaise</t>
+          <t>Club Poulet Mayonnaise</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>CLUB Jambon Beurre Fleur DE SEL DE Guérande Salade</t>
+          <t>Club Jambon Beurre Fleur de Sel de Guérande Salade</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chips Nature SEL Guerande 90g</t>
+          <t>Chips Nature Sel Guerande 90g</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Spaghetti ALLA Bolognese</t>
+          <t>Spaghetti Alla Bolognese</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Chips DE Pomme Nature</t>
+          <t>Chips de Pomme Nature</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>CLUB THON A LA Nicoise</t>
+          <t>Club Thon a la Nicoise</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Gnochi Cacio E PEPE</t>
+          <t>Gnochi Cacio E Pepe</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SUGARY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Red Bull Sugar FREE</t>
+          <t>Red Bull Sugar Free</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cable USB 3 EN 1 Tekmee</t>
+          <t>Cable USB 3 en 1 Tekmee</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>BOB Artengo Marine Retro</t>
+          <t>Bob Artengo Marine Retro</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Red Bull Taurine NVL Recette BTE 25cl</t>
+          <t>Red Bull Taurine Nvl Recette BTE 25cl</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Casquette DE GOLF Adulte Ww100 BLEU Marine</t>
+          <t>Casquette de Golf Adulte Ww100 Bleu Marine</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Chaussettes de Sport Enfant Mi / Hautes Artengo Rs 500 Noir (lot de 3) / 31 / 34</t>
+          <t>Chaussettes de Sport Enfant Mi / Hautes Artengo RS 500 Noir (lot de 3) / 31 / 34</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO 33cl</t>
+          <t>Coca-Cola Zero 33cl</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>IGP Cabernet Sauvignon 37,5cl</t>
+          <t>Igp Cabernet Sauvignon 37,5cl</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>100g Choc Noir MPG M. Havelaar</t>
+          <t>100g Choc Noir Mpg M. Havelaar</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Sac de Courses DD Paris (tour Eiffel)</t>
+          <t>Sac de Courses Dd Paris (tour Eiffel)</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>SOUVENIRS</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Le Béret Français - BLEU Royal (extensible Tour de Tête 55 à 62 Cm)</t>
+          <t>Le Béret Français - Bleu Royal (extensible Tour de Tête 55 à 62 Cm)</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>PAP</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>BLOC A Colorier - LA Ferme</t>
+          <t>Bloc a Colorier - la Ferme</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Pastille DES Alpes</t>
+          <t>Pastille des Alpes</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Nature - SO Chips</t>
+          <t>Nature - So Chips</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Herbes de Provence - SO Chips</t>
+          <t>Herbes de Provence - So Chips</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>PAP</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>COSMETIQUE</t>
+          <t>SOS</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>SUGARY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Evian 33 CL</t>
+          <t>Evian 33 Cl</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Pasta BOX Fromages Italien</t>
+          <t>Pasta Box Fromages Italien</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pasta BOX Bolognese</t>
+          <t>Pasta Box Bolognese</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>SOUVENIRS</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Gelée Active Nettoyante – 140ml NEW</t>
+          <t>Gelée Active Nettoyante – 140ml New</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Pasta BOX Jambon CRU</t>
+          <t>Pasta Box Jambon Cru</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Toblerone LAIT 50g</t>
+          <t>Toblerone Lait 50g</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Mousse AU Chocolat A L'Ancienne</t>
+          <t>Mousse au Chocolat a L'Ancienne</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Tablette DE Chocolat NOIR 71% Cacao LE Chocolat DES Français BIO 80g</t>
+          <t>Tablette de Chocolat Noir 71% Cacao le Chocolat des Français BIO 80g</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Biscuit Sucre PUR Beurre 50g</t>
+          <t>Biscuit Sucre Pur Beurre 50g</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>MF Compact XL Towel BLUE Petrol</t>
+          <t>Mf Compact XL Towel Blue Petrol</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Maillot DE BAIN Natation Garçon - Swimshort 100 Basic - Marine</t>
+          <t>Maillot de Bain Natation Garçon - Swimshort 100 Basic - Marine</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Fanta Orange BTE SLIM 33cl</t>
+          <t>Fanta Orange BTE Slim 33cl</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>COCA ZERO 50cl</t>
+          <t>Coca Zero 50cl</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Brassards Piscine Junior Orange 30-60 KG</t>
+          <t>Brassards Piscine Junior Orange 30-60 Kg</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>COCA Cherry 50cl</t>
+          <t>Coca Cherry 50cl</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Maillot DE BAIN Natation Garçon - Boxer 100 Basic - BLEU</t>
+          <t>Maillot de Bain Natation Garçon - Boxer 100 Basic - Bleu</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte - Aquashoes 100 GRI 36-37 UK 3-4</t>
+          <t>Chaussures Aquatiques Adulte - Aquashoes 100 Gri 36-37 UK 3-4</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO 33cl</t>
+          <t>Coca-Cola Zero 33cl</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Boîte MTL Caramels BS 150g</t>
+          <t>Boîte Mtl Caramels Bs 150g</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>SUGARY FOOD</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Dry</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Bière Bacchante Triple DES FIZ</t>
+          <t>Bière Bacchante Triple des Fiz</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -20150,7 +20150,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Special K Chocolat NOIR</t>
+          <t>Special K Chocolat Noir</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Biscuit Sucre PUR Beurre 50g</t>
+          <t>Biscuit Sucre Pur Beurre 50g</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO 33cl</t>
+          <t>Coca-Cola Zero 33cl</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>WRAP Veggie ŒUF Parmesan Tomates</t>
+          <t>Wrap Veggie Œuf Parmesan Tomates</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Tablette DE Chocolat NOIR AUX Noisettes - Chocolat DES Français 80g</t>
+          <t>Tablette de Chocolat Noir aux Noisettes - Chocolat des Français 80g</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>CLUB Poulet Cajun Pousses D'Épinard</t>
+          <t>Club Poulet Cajun Pousses D'Épinard</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Red Bull Regular 25 CL</t>
+          <t>Red Bull Regular 25 Cl</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -21242,7 +21242,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>MEGA Sandwich CLUB Poulet ROTI Mayonnaise 230g</t>
+          <t>Mega Sandwich Club Poulet Roti Mayonnaise 230g</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Sandwich MEGA CLUB Poulet Rotis 230g</t>
+          <t>Sandwich Mega Club Poulet Rotis 230g</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Spray Répulsif ANTI Moustique ET Tique Icaridine - 60 ML</t>
+          <t>Spray Répulsif Anti Moustique et Tique Icaridine - 60 Ml</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Tongs Homme TO 100 NOIR</t>
+          <t>Tongs Homme To 100 Noir</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>FUSE TEA ICE TEA Peche BTE 33cl</t>
+          <t>Fuse Tea Ice Tea Peche BTE 33cl</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -21570,7 +21570,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Plein Fruit BIO Pomme 23.5 CL</t>
+          <t>Plein Fruit BIO Pomme 23.5 Cl</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Serviette DE Plage Verte XL</t>
+          <t>Serviette de Plage Verte XL</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte - Aquashoes 100 GRI 40-41 UK 6.5-7</t>
+          <t>Chaussures Aquatiques Adulte - Aquashoes 100 Gri 40-41 UK 6.5-7</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte - Aquashoes 100 GRI 38-39 UK 5-5.5</t>
+          <t>Chaussures Aquatiques Adulte - Aquashoes 100 Gri 38-39 UK 5-5.5</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -21864,7 +21864,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Serviette DE BAIN Microfibre VERT Taille L 80 X 130 CM</t>
+          <t>Serviette de Bain Microfibre Vert Taille L 80 x 130 Cm</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Coca-Cola Cherry SLIM BTE 33cl</t>
+          <t>Coca-Cola Cherry Slim BTE 33cl</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -22032,7 +22032,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Coca-Cola SLIM BTE 33cl</t>
+          <t>Coca-Cola Slim BTE 33cl</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Maillot DE BAIN Natation Garçon / Swimshort 100 Basic / Marine</t>
+          <t>Maillot de Bain Natation Garçon / Swimshort 100 Basic / Marine</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SAC A DOS 10l</t>
+          <t>Sac a Dos 10l</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -22232,7 +22232,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Short BLEU Marine L</t>
+          <t>Short Bleu Marine L</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>Short BLEU Marine S</t>
+          <t>Short Bleu Marine S</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Cake à la Banane et aux Pépites de Chocolat MPG 40g</t>
+          <t>Cake à la Banane et aux Pépites de Chocolat Mpg 40g</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>BLOC A Colorier - LES Pirates</t>
+          <t>Bloc a Colorier - les Pirates</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>PAP</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -23996,7 +23996,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>PAP</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>COSMETIQUE</t>
+          <t>SOS</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -24725,7 +24725,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -24846,7 +24846,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Pasta BOX Carbonara</t>
+          <t>Pasta Box Carbonara</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>SOUVENIRS</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Tranche DE Panettone Classique (raisin Orange) 70g</t>
+          <t>Tranche de Panettone Classique (raisin Orange) 70g</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Tablette DE Chocolat NOIR Amandes Caramel ET SEL - Chocolat DES Français 80g</t>
+          <t>Tablette de Chocolat Noir Amandes Caramel et Sel - Chocolat des Français 80g</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -25812,7 +25812,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Blast Snack Chocolat NOIR SEL DE MER Amandes</t>
+          <t>Blast Snack Chocolat Noir Sel de Mer Amandes</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Vitao Green TEA</t>
+          <t>Vitao Green Tea</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -25938,7 +25938,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>Madeleine Coque Chocolat NOIR 60g</t>
+          <t>Madeleine Coque Chocolat Noir 60g</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -26170,7 +26170,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>SUGARY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26296,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>SALTY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
@@ -26321,7 +26321,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Gourde Randonnée Mh500 Bouchon Ouverture Rapide 1 Litre Aluminium BLEU</t>
+          <t>Gourde Randonnée Mh500 Bouchon Ouverture Rapide 1 Litre Aluminium Bleu</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Plein Fruit BIO Orange 23.5 CL</t>
+          <t>Plein Fruit BIO Orange 23.5 Cl</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Boxer DE BAIN Natation Homme - Boxer 100 PLUS - NOIR BLEU</t>
+          <t>Boxer de Bain Natation Homme - Boxer 100 Plus - Noir Bleu</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>TOUR DE COU</t>
+          <t>Tour de Cou</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO SLIM BTE 33cl</t>
+          <t>Coca-Cola Zero Slim BTE 33cl</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -26852,7 +26852,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte - Aquashoes 100 GRI 42-43 UK 8-8.5</t>
+          <t>Chaussures Aquatiques Adulte - Aquashoes 100 Gri 42-43 UK 8-8.5</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
@@ -27072,7 +27072,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>Casquette DE GOLF Adulte Mw500 Bleue</t>
+          <t>Casquette de Golf Adulte Mw500 Bleue</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -28374,7 +28374,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>Peluche DOGZ &amp; CATS Sonores</t>
+          <t>Peluche Dogz &amp; Cats Sonores</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -28416,7 +28416,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Feutres DE Couleur</t>
+          <t>Feutres de Couleur</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -28490,7 +28490,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -29718,7 +29718,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Nature / SO Chips</t>
+          <t>Nature / So Chips</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -30592,7 +30592,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Badoit Verte 50 CL</t>
+          <t>Badoit Verte 50 Cl</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -30634,7 +30634,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Graines DE Folies A Croquer SEL 45g</t>
+          <t>Graines de Folies a Croquer Sel 45g</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Tablettede Chocolat NOIR AUX Noisettes - Chocolat DES Français 80g</t>
+          <t>Tablettede Chocolat Noir aux Noisettes - Chocolat des Français 80g</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -30718,7 +30718,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Tampons LOVE &amp; Green BIO X 2</t>
+          <t>Tampons Love &amp; Green BIO x 2</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -30844,7 +30844,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>Red Bull Regular 25 CL</t>
+          <t>Red Bull Regular 25 Cl</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>KIT Rasage</t>
+          <t>Kit Rasage</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Burger Bistrot BŒUF Charolais</t>
+          <t>Burger Bistrot Bœuf Charolais</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Risotto Champignons ET Cepes</t>
+          <t>Risotto Champignons et Cepes</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Sandwich Complet Poulet ROTI 125g</t>
+          <t>Sandwich Complet Poulet Roti 125g</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -31558,7 +31558,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Biscuite SALE Tomate 35g</t>
+          <t>Biscuite Sale Tomate 35g</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -31684,7 +31684,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>CLUB Saumon FUME Citron Aneth</t>
+          <t>Club Saumon Fume Citron Aneth</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -31810,7 +31810,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>Maillot DE BAIN DE Natation 1 Pièce Fille Basic Violet</t>
+          <t>Maillot de Bain de Natation 1 Pièce Fille Basic Violet</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>Brassards Piscine Enfant Orange 11-30 KG</t>
+          <t>Brassards Piscine Enfant Orange 11-30 Kg</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -31894,7 +31894,7 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>Maillot DE BAIN DE Natation 1 Pièce Femme HEVA U NOIR</t>
+          <t>Maillot de Bain de Natation 1 Pièce Femme Heva U Noir</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>Lunettes DE Natation Verres Clairs Xbase Taille S BLEU Jaune</t>
+          <t>Lunettes de Natation Verres Clairs Xbase Taille S Bleu Jaune</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
@@ -31978,7 +31978,7 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>SET Raquettes Beach Tennis Woody Racket Yellow</t>
+          <t>Set Raquettes Beach Tennis Woody Racket Yellow</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -32104,7 +32104,7 @@
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO SLIM BTE 33cl</t>
+          <t>Coca-Cola Zero Slim BTE 33cl</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -32230,7 +32230,7 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Maillot DE BAIN Natation Garçon - Swimshort 100 Basic - Orange</t>
+          <t>Maillot de Bain Natation Garçon - Swimshort 100 Basic - Orange</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -32314,7 +32314,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>Grand Parapluie BLEU</t>
+          <t>Grand Parapluie Bleu</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -32356,7 +32356,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>Frite DE Plage</t>
+          <t>Frite de Plage</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -32430,7 +32430,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
@@ -32546,7 +32546,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -32571,7 +32571,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -32608,7 +32608,7 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>SAC Banane</t>
+          <t>Sac Banane</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>Boardshort Hendaia ECO NT Rouge</t>
+          <t>Boardshort Hendaia Eco NT Rouge</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>Boardshort Hendaia ECO NT Turquoise</t>
+          <t>Boardshort Hendaia Eco NT Turquoise</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -32934,7 +32934,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
@@ -33574,7 +33574,7 @@
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>Petit Financ. Amande 210g MPG</t>
+          <t>Petit Financ. Amande 210g Mpg</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -33742,7 +33742,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>Coca-Cola ZERO 33cl</t>
+          <t>Coca-Cola Zero 33cl</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
@@ -34330,7 +34330,7 @@
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>LEGO Aventures du Marais Minecraft</t>
+          <t>Lego Aventures du Marais Minecraft</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
@@ -34540,7 +34540,7 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>BLOC A Colorier - LES Licornes</t>
+          <t>Bloc a Colorier - les Licornes</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -34582,7 +34582,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>PALM Sushi</t>
+          <t>Palm Sushi</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>Jeu UNO</t>
+          <t>Jeu Uno</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
@@ -34876,7 +34876,7 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>Chocolat Savoie -Chocolaterie HAUT Giffre</t>
+          <t>Chocolat Savoie -Chocolaterie Haut Giffre</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Carres LOVE</t>
+          <t>Carres Love</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -36136,7 +36136,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>Carte SIM Prépayée</t>
+          <t>Carte Sim Prépayée</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -36168,7 +36168,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
@@ -36346,7 +36346,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>Suedois Poulet ROTI Tendoori 125g</t>
+          <t>Suedois Poulet Roti Tendoori 125g</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>Gourde EN Verre Novotel</t>
+          <t>Gourde en Verre Novotel</t>
         </is>
       </c>
       <c r="H860" t="inlineStr">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>Masque Easybreath DE Surface Adulte - 500 BLEU</t>
+          <t>Masque Easybreath de Surface Adulte - 500 Bleu</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
@@ -36840,7 +36840,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
@@ -37008,7 +37008,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
@@ -37018,7 +37018,7 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte / Aquashoes 100 GRI 36 / 37 UK 3 / 4</t>
+          <t>Chaussures Aquatiques Adulte / Aquashoes 100 Gri 36 / 37 UK 3 / 4</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
@@ -37102,7 +37102,7 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>Grand Parapluie NOIR ET GRIS</t>
+          <t>Grand Parapluie Noir et Gris</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
@@ -37176,7 +37176,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
@@ -37186,7 +37186,7 @@
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>Chaussettes Sports DE Raquettes Basses Enfant Artengo RS 100 Blanc LOT DE 3</t>
+          <t>Chaussettes Sports de Raquettes Basses Enfant Artengo RS 100 Blanc Lot de 3</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
@@ -37808,7 +37808,7 @@
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>Barquette DE Fraise 500g</t>
+          <t>Barquette de Fraise 500g</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
@@ -38386,7 +38386,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>SOUVENIRS</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>Le Béret Français - ECRU (extensible Tour de Tête 55 à 62 Cm)</t>
+          <t>Le Béret Français - Ecru (extensible Tour de Tête 55 à 62 Cm)</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>LEGO City Pompier</t>
+          <t>Lego City Pompier</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>BLOC A Colorier - LES Animaux</t>
+          <t>Bloc a Colorier - les Animaux</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
@@ -39698,7 +39698,7 @@
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>TIRE Bouchon</t>
+          <t>Tire Bouchon</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
@@ -39804,7 +39804,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -39814,7 +39814,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>SALTY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F940" t="inlineStr">
@@ -39829,7 +39829,7 @@
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -39908,7 +39908,7 @@
       </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>PATE Basque</t>
+          <t>Pate Basque</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>KIT Dentaire Colgate</t>
+          <t>Kit Dentaire Colgate</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
@@ -40370,7 +40370,7 @@
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>Kombucha MATE Gingembre Citron BIO</t>
+          <t>Kombucha Mate Gingembre Citron BIO</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
@@ -40538,7 +40538,7 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>CLUB Poulet</t>
+          <t>Club Poulet</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
@@ -40782,7 +40782,7 @@
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>Tongs Femme 100 NOIR</t>
+          <t>Tongs Femme 100 Noir</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
@@ -40804,7 +40804,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -40824,12 +40824,12 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>Lunettes DE Natation Verres Clairs Xbase Taille S ROSE</t>
+          <t>Lunettes de Natation Verres Clairs Xbase Taille S Rose</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -40866,7 +40866,7 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>Spray Protection Solaire Active SPF 30 50 ML</t>
+          <t>Spray Protection Solaire Active SPF 30 50 Ml</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -40950,7 +40950,7 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>Coca-Cola Cherry SLIM BTE 33cl</t>
+          <t>Coca-Cola Cherry Slim BTE 33cl</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
@@ -41234,7 +41234,7 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
@@ -41244,7 +41244,7 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>Chaussures Aquatiques Adulte / Aquashoes 100 GRI 42 / 43 UK 8 / 8.5</t>
+          <t>Chaussures Aquatiques Adulte / Aquashoes 100 Gri 42 / 43 UK 8 / 8.5</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -41404,7 +41404,7 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>Short BLEU Marine XXL</t>
+          <t>Short Bleu Marine XXL</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
@@ -41720,7 +41720,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -41730,7 +41730,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>SALTY FOOD</t>
+          <t>COSMETIQUE</t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
@@ -41745,7 +41745,7 @@
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -42202,7 +42202,7 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>Mini Moelleux Choc 210g MPG</t>
+          <t>Mini Moelleux Choc 210g Mpg</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
@@ -42370,7 +42370,7 @@
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>MPG Mousse Chocolat 2x90g</t>
+          <t>Mpg Mousse Chocolat 2x90g</t>
         </is>
       </c>
       <c r="H1001" t="inlineStr">
@@ -43158,7 +43158,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>ACCESSOIRES</t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
@@ -43494,7 +43494,7 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>PAP</t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
@@ -43652,7 +43652,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>NON-F&amp;B</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>PAP</t>
+          <t>NonF&amp;B</t>
         </is>
       </c>
     </row>
@@ -43746,7 +43746,7 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>ACCESSOIRES</t>
+          <t>JEU_ENFANTS</t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
@@ -44026,7 +44026,7 @@
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>Gourde Novotel JEUX Olympiques Paris 2024</t>
+          <t>Gourde Novotel Jeux Olympiques Paris 2024</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="G1050" t="inlineStr">
         <is>
-          <t>Gourde EN Varre Novotel</t>
+          <t>Gourde en Varre Novotel</t>
         </is>
       </c>
       <c r="H1050" t="inlineStr">
